--- a/out/Attention-mamba2_repeat_3_000001.xlsx
+++ b/out/Attention-mamba2_repeat_3_000001.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.931760215741336</v>
+        <v>4.447630813187695</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.931760215741336</v>
+        <v>4.447630813187695</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.931760215741336</v>
+        <v>5.047630813187695</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.1128374620163213</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.1128374620163213</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.931760215741336</v>
+        <v>5.047630813187695</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA9" t="n">
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.1128374620163213</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA10" t="n">
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.1128374620163213</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.501156825476262</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.331760215741336</v>
+        <v>5.047630813187695</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.331760215741336</v>
+        <v>5.047630813187695</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.931760215741336</v>
+        <v>5.047630813187695</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.931760215741336</v>
+        <v>5.047630813187695</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.1128374620163213</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.931760215741336</v>
+        <v>4.447630813187695</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.931760215741336</v>
+        <v>5.047630813187695</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.1128374620163213</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.501156825476262</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.331760215741336</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.331760215741336</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.501156825476262</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.331760215741336</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.331760215741336</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.501156825476262</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0002226076271173079</v>
+        <v>-4.177861043880694e-05</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.09584827399105236</v>
+        <v>0.01798865665844843</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.331760215741336</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.1919525566547976</v>
+        <v>0.03602532028547244</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.370312572099705</v>
+        <v>0.06949969403132268</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.501156825476262</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.8369759782074536</v>
+        <v>0.1570820532903005</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1139107320552014</v>
+        <v>0.02137849547928601</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.501156825476262</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.6940144289015532</v>
+        <v>0.1302513694696855</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.02311333487591909</v>
+        <v>0.004335728123028865</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.501156825476262</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.626152164128749</v>
+        <v>0.1175130132573326</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02001681743770138</v>
+        <v>0.003753689126462496</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.501156825476262</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.6430476285130486</v>
+        <v>0.1206808269409142</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.009786117585672974</v>
+        <v>0.001832546535206301</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.501156825476262</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.6425765098619773</v>
+        <v>0.1205883541637983</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.00466752407647265</v>
+        <v>0.0008716411537726466</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.501156825476262</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.6421157506060451</v>
+        <v>0.1204978204473769</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.001941815580033225</v>
+        <v>0.0003602018931946799</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.501156825476262</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.6413258242877398</v>
+        <v>0.1203454650245428</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001343881764565661</v>
+        <v>0.000248108248728568</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.501156825476262</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.6420707819277921</v>
+        <v>0.1204813641765444</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0005581068586826616</v>
+        <v>0.0001006630718809571</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.501156825476262</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.6418415200178099</v>
+        <v>0.1204341793883636</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0002869909940538464</v>
+        <v>4.979007211079042e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.6418568321993507</v>
+        <v>0.1204330102535854</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001099452349326009</v>
+        <v>1.651942754445953e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.6417887191262143</v>
+        <v>0.1204160510843939</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>5.741702548561189e-05</v>
+        <v>7.025298488053667e-06</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.6417940530204922</v>
+        <v>0.1204130328038612</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>2.605694527035538e-05</v>
+        <v>6.467173218827975e-07</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.501156825476262</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.6417881060215018</v>
+        <v>0.120407852651132</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>9.386291621141726e-06</v>
+        <v>-2.335871922010791e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.501156825476262</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.6417813189624618</v>
+        <v>0.1204024957344094</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>1.456405945771008e-06</v>
+        <v>-3.616484440191926e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.501156825476262</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.6417742941239011</v>
+        <v>0.120397061840432</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-2.106181251314092e-06</v>
+        <v>-4.586597321616299e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.501156825476262</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.6417686168923313</v>
+        <v>0.1203919172664983</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-4.04640701416283e-06</v>
+        <v>-4.68213567138761e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.6417629443820471</v>
+        <v>0.1203867249807813</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.634963333793937e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.6417574007139446</v>
+        <v>0.1203865894721756</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-4.777674021158921e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.6417524795602232</v>
+        <v>0.1203866293276478</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.6417525194156954</v>
+        <v>0.1203866691831201</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.641752511444601</v>
+        <v>0.1203866612120257</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.6417526708664901</v>
+        <v>0.1203868206339148</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.6417525752133566</v>
+        <v>0.1203867249807813</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.501156825476262</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.6417529259415129</v>
+        <v>0.1203870757089376</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.501156825476262</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.6417526788375846</v>
+        <v>0.1203868286050092</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.331760215741336</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.6417526389821123</v>
+        <v>0.120386788749537</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>1.501156825476262</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.6417525752133566</v>
+        <v>0.1203867249807813</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>1.501156825476262</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.6417526469532068</v>
+        <v>0.1203867967206314</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>1.501156825476262</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.6417525752133566</v>
+        <v>0.1203867249807813</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.331760215741336</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.6417526788375846</v>
+        <v>0.1203868286050092</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.6417527744907182</v>
+        <v>0.1203869242581429</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.6417527107219624</v>
+        <v>0.1203868604893871</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.6417526708664901</v>
+        <v>0.1203868206339148</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.331760215741336</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.6417526469532068</v>
+        <v>0.1203867967206314</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>1.501156825476262</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.6417523998492786</v>
+        <v>0.1203865496167033</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.6417523201383338</v>
+        <v>0.1203864699057585</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.501156825476262</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.6417523679649005</v>
+        <v>0.1203865177323252</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.501156825476262</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.6417524875313176</v>
+        <v>0.1203866372987423</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.501156825476262</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.6417524715891287</v>
+        <v>0.1203866213565534</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.501156825476262</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.6417524875313176</v>
+        <v>0.1203866372987423</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.501156825476262</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.6417524715891287</v>
+        <v>0.1203866213565534</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.501156825476262</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.6417525273867899</v>
+        <v>0.1203866771542146</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.6417525273867899</v>
+        <v>0.1203866771542146</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.6417525273867899</v>
+        <v>0.1203866771542146</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.6417526788375846</v>
+        <v>0.1203868286050092</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.6417528940571351</v>
+        <v>0.1203870438245598</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.6417528063750961</v>
+        <v>0.1203869561425208</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.6417527585485293</v>
+        <v>0.120386908315954</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.501156825476262</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.6417528063750961</v>
+        <v>0.1203869561425208</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.501156825476262</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.6417526230399234</v>
+        <v>0.1203867728073481</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.501156825476262</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.6417526310110179</v>
+        <v>0.1203867807784425</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.501156825476262</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.6417526389821123</v>
+        <v>0.120386788749537</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.501156825476262</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.6417526469532068</v>
+        <v>0.1203867967206314</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.501156825476262</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.6417526469532068</v>
+        <v>0.1203867967206314</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.501156825476262</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.641752686808679</v>
+        <v>0.1203868365761037</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.6417527505774349</v>
+        <v>0.1203869003448596</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.6417528621727573</v>
+        <v>0.1203870119401819</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.641752909999324</v>
+        <v>0.1203870597667487</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.6417528701438517</v>
+        <v>0.1203870199112764</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.6417527984040017</v>
+        <v>0.1203869481714263</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.6417529179704184</v>
+        <v>0.1203870677378431</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.6417527585485293</v>
+        <v>0.120386908315954</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.6417525273867899</v>
+        <v>0.1203866771542146</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.6417524795602232</v>
+        <v>0.1203866293276478</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.501156825476262</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.641752511444601</v>
+        <v>0.1203866612120257</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.501156825476262</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.6417525752133566</v>
+        <v>0.1203867249807813</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.501156825476262</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.6417525752133566</v>
+        <v>0.1203867249807813</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.501156825476262</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.6417524955024121</v>
+        <v>0.1203866452698368</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.501156825476262</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.641752375935995</v>
+        <v>0.1203865257034197</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.501156825476262</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.6417523360805227</v>
+        <v>0.1203864858479474</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.501156825476262</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.6417524795602232</v>
+        <v>0.1203866293276478</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.641752615068829</v>
+        <v>0.1203867648362536</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.64175259912664</v>
+        <v>0.1203867488940647</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.6417525752133566</v>
+        <v>0.1203867249807813</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.6417525353578843</v>
+        <v>0.120386685125309</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.6417524317336565</v>
+        <v>0.1203865815010811</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.6417523121672394</v>
+        <v>0.1203864619346641</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.6417524317336565</v>
+        <v>0.1203865815010811</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.6417524795602232</v>
+        <v>0.1203866293276478</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.501156825476262</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.6417525752133566</v>
+        <v>0.1203867249807813</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.501156825476262</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.6417524556469398</v>
+        <v>0.1203866054143645</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.501156825476262</v>
+        <v>-0.7128374620163214</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.6417524636180343</v>
+        <v>0.1203866133854589</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_3_000001.xlsx
+++ b/out/Attention-mamba2_repeat_3_000001.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.140787574607127</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.140787574607127</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.140787574607127</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.140787574607127</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.140787574607127</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.140787574607127</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.140787574607127</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.140787574607127</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.140787574607127</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.140787574607127</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.140787574607127</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.140787574607127</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.140787574607127</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.140787574607127</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.2947854768329915</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.501156825476262</v>
+        <v>-0.2947854768329914</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.331760215741336</v>
+        <v>-0.2947854768329914</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.331760215741336</v>
+        <v>-0.9407875746071271</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.9407875746071271</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.140787574607127</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.140787574607127</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.140787574607127</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.140787574607127</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.140787574607127</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.140787574607127</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.140787574607127</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.140787574607127</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.140787574607127</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.2947854768329914</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.501156825476262</v>
+        <v>-0.2947854768329913</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.331760215741336</v>
+        <v>-0.2947854768329913</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.331760215741336</v>
+        <v>-0.9407875746071271</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.9407875746071271</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.140787574607127</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.140787574607127</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.140787574607127</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.140787574607127</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.4947854768329913</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.501156825476262</v>
+        <v>-0.2947854768329914</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.331760215741336</v>
+        <v>-0.2947854768329914</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.331760215741336</v>
+        <v>-0.9407875746071271</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.501156825476262</v>
+        <v>-0.9407875746071271</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0002226076271173079</v>
+        <v>-2.31607684798073e-05</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.09584827399105236</v>
+        <v>0.009972354459690098</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.331760215741336</v>
+        <v>-0.4947854768329913</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.1919525566547976</v>
+        <v>0.01997132249682862</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.370312572099705</v>
+        <v>0.03852765181264967</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.501156825476262</v>
+        <v>0.3512166209411444</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.8369759782074536</v>
+        <v>0.08708142989710253</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1139107320552014</v>
+        <v>0.01185183068427846</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.501156825476262</v>
+        <v>0.9972187187152801</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.6940144289015532</v>
+        <v>0.07220700984759769</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.02311333487591909</v>
+        <v>0.002401416990871525</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.501156825476262</v>
+        <v>0.9972187187152801</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.626152164128749</v>
+        <v>0.06514287970358738</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02001681743770138</v>
+        <v>0.002078387687239212</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.501156825476262</v>
+        <v>0.9972187187152801</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.6430476285130486</v>
+        <v>0.06689682790407654</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.009786117585672974</v>
+        <v>0.001013525793800064</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.501156825476262</v>
+        <v>0.9972187187152801</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.6425765098619773</v>
+        <v>0.06684332705114317</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.00466752407647265</v>
+        <v>0.0004814289328860417</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.501156825476262</v>
+        <v>0.9972187187152801</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.6421157506060451</v>
+        <v>0.06679088396141189</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.001941815580033225</v>
+        <v>0.0001976425139068041</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.501156825476262</v>
+        <v>0.9972187187152801</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.6413258242877398</v>
+        <v>0.06670418159370729</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001343881764565661</v>
+        <v>0.0001354442111847542</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.501156825476262</v>
+        <v>0.9972187187152801</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.6420707819277921</v>
+        <v>0.06677724401964061</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0005581068586826616</v>
+        <v>5.363011915345791e-05</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.501156825476262</v>
+        <v>0.3512166209411443</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.6418415200178099</v>
+        <v>0.06674890737445187</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0002869909940538464</v>
+        <v>2.506772249982401e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.931760215741336</v>
+        <v>0.1512166209411443</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.6418568321993507</v>
+        <v>0.06674602046867716</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001099452349326009</v>
+        <v>7.071873988355347e-06</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.1512166209411443</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.6417887191262143</v>
+        <v>0.06673439215506008</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>5.741702548561189e-05</v>
+        <v>1.298965874694778e-06</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7972187187152801</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.6417940530204922</v>
+        <v>0.06673047802515723</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>2.605694527035538e-05</v>
+        <v>-1.611969606870321e-06</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.501156825476262</v>
+        <v>0.7972187187152801</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.6417881060215018</v>
+        <v>0.06672537471617641</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>9.386291621141726e-06</v>
+        <v>-3.401523153206475e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.501156825476262</v>
+        <v>0.9972187187152801</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.6417813189624618</v>
+        <v>0.06672017969676969</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>1.456405945771008e-06</v>
+        <v>-4.538828146730642e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.501156825476262</v>
+        <v>0.9972187187152801</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.6417742941239011</v>
+        <v>0.06671496332559386</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-2.106181251314092e-06</v>
+        <v>-4.586597321616299e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.501156825476262</v>
+        <v>0.3512166209411443</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.6417686168923313</v>
+        <v>0.06670986657822668</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-4.04640701416283e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.931760215741336</v>
+        <v>0.1512166209411443</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.6417629443820471</v>
+        <v>0.06670977092509321</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.634963333793937e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.4947854768329915</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.6417574007139446</v>
+        <v>0.06670963541648746</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-4.777674021158921e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.931760215741336</v>
+        <v>0.1512166209411442</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.6417524795602232</v>
+        <v>0.06670967527195974</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.4947854768329915</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.6417525194156954</v>
+        <v>0.06670971512743203</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.931760215741336</v>
+        <v>0.1512166209411442</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.641752511444601</v>
+        <v>0.06670970715633756</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.4947854768329915</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.6417526708664901</v>
+        <v>0.06670986657822668</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.931760215741336</v>
+        <v>0.1512166209411442</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.6417525752133566</v>
+        <v>0.06670977092509321</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>1.501156825476262</v>
+        <v>0.1512166209411442</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.6417529259415129</v>
+        <v>0.06671012165324949</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.501156825476262</v>
+        <v>0.3512166209411443</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.6417526788375846</v>
+        <v>0.06670987454932113</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.331760215741336</v>
+        <v>0.3512166209411443</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.6417526389821123</v>
+        <v>0.06670983469384885</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>1.501156825476262</v>
+        <v>0.3512166209411443</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.6417525752133566</v>
+        <v>0.06670977092509321</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>1.501156825476262</v>
+        <v>0.9972187187152801</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.6417526469532068</v>
+        <v>0.06670984266494331</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>1.501156825476262</v>
+        <v>0.3512166209411443</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.6417525752133566</v>
+        <v>0.06670977092509321</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.331760215741336</v>
+        <v>-0.2947854768329914</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.6417526788375846</v>
+        <v>0.06670987454932113</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.4947854768329915</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.6417527744907182</v>
+        <v>0.06670997020245484</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.1512166209411443</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.6417527107219624</v>
+        <v>0.06670990643369895</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.1512166209411443</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.6417526708664901</v>
+        <v>0.06670986657822668</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.331760215741336</v>
+        <v>0.3512166209411444</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.6417526469532068</v>
+        <v>0.06670984266494331</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>1.501156825476262</v>
+        <v>0.3512166209411444</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.6417523998492786</v>
+        <v>0.06670959556101519</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.9972187187152801</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.6417523201383338</v>
+        <v>0.0667095158500704</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.501156825476262</v>
+        <v>0.9972187187152801</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.6417523679649005</v>
+        <v>0.06670956367663713</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.501156825476262</v>
+        <v>0.9972187187152801</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.6417524875313176</v>
+        <v>0.06670968324305419</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.501156825476262</v>
+        <v>0.9972187187152801</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.6417524715891287</v>
+        <v>0.06670966730086529</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.501156825476262</v>
+        <v>0.9972187187152801</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.6417524875313176</v>
+        <v>0.06670968324305419</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.501156825476262</v>
+        <v>0.9972187187152801</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.6417524715891287</v>
+        <v>0.06670966730086529</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.501156825476262</v>
+        <v>0.3512166209411444</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.6417525273867899</v>
+        <v>0.06670972309852648</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.4947854768329915</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.6417525273867899</v>
+        <v>0.06670972309852648</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.4947854768329915</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.6417525273867899</v>
+        <v>0.06670972309852648</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.4947854768329913</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.6417526788375846</v>
+        <v>0.06670987454932113</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.931760215741336</v>
+        <v>0.1512166209411444</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.6417528940571351</v>
+        <v>0.06671008976887166</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.1512166209411444</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.6417528063750961</v>
+        <v>0.06671000208683266</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.9972187187152801</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.6417527585485293</v>
+        <v>0.06670995426026592</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.501156825476262</v>
+        <v>0.9972187187152801</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.6417528063750961</v>
+        <v>0.06671000208683266</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.501156825476262</v>
+        <v>0.9972187187152801</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.6417526230399234</v>
+        <v>0.06670981875165995</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.501156825476262</v>
+        <v>0.9972187187152801</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.6417526310110179</v>
+        <v>0.0667098267227544</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.501156825476262</v>
+        <v>0.9972187187152801</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.6417526389821123</v>
+        <v>0.06670983469384885</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.501156825476262</v>
+        <v>0.9972187187152801</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.6417526469532068</v>
+        <v>0.06670984266494331</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.501156825476262</v>
+        <v>0.9972187187152801</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.6417526469532068</v>
+        <v>0.06670984266494331</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.501156825476262</v>
+        <v>0.9972187187152801</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.641752686808679</v>
+        <v>0.06670988252041558</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.9972187187152801</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.6417527505774349</v>
+        <v>0.06670994628917147</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7972187187152801</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.6417528621727573</v>
+        <v>0.06671005788449384</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7972187187152801</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.641752909999324</v>
+        <v>0.06671010571106058</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7972187187152801</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.6417528701438517</v>
+        <v>0.06671006585558829</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7972187187152801</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.6417527984040017</v>
+        <v>0.06670999411573819</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.1512166209411444</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.6417529179704184</v>
+        <v>0.06671011368215503</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.931760215741336</v>
+        <v>0.1512166209411444</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.6417527585485293</v>
+        <v>0.06670995426026592</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.1512166209411444</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.6417525273867899</v>
+        <v>0.06670972309852648</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7972187187152801</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.6417524795602232</v>
+        <v>0.06670967527195974</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.501156825476262</v>
+        <v>0.7972187187152801</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.641752511444601</v>
+        <v>0.06670970715633756</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.501156825476262</v>
+        <v>0.9972187187152801</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.6417525752133566</v>
+        <v>0.06670977092509321</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>1.501156825476262</v>
+        <v>0.9972187187152801</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.6417525752133566</v>
+        <v>0.06670977092509321</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.501156825476262</v>
+        <v>0.9972187187152801</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.6417524955024121</v>
+        <v>0.06670969121414866</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.501156825476262</v>
+        <v>0.9972187187152801</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.641752375935995</v>
+        <v>0.06670957164773159</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.501156825476262</v>
+        <v>0.9972187187152801</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.6417523360805227</v>
+        <v>0.06670953179225932</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.501156825476262</v>
+        <v>0.9972187187152801</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.6417524795602232</v>
+        <v>0.06670967527195974</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.9972187187152801</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.641752615068829</v>
+        <v>0.06670981078056548</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7972187187152801</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.64175259912664</v>
+        <v>0.06670979483837658</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7972187187152801</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.6417525752133566</v>
+        <v>0.06670977092509321</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7972187187152801</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.6417525353578843</v>
+        <v>0.06670973106962093</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.1512166209411444</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.6417524317336565</v>
+        <v>0.06670962744539301</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.931760215741336</v>
+        <v>0.1512166209411444</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.6417523121672394</v>
+        <v>0.06670950787897595</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.1512166209411444</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.6417524317336565</v>
+        <v>0.06670962744539301</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7972187187152801</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.6417524795602232</v>
+        <v>0.06670967527195974</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.501156825476262</v>
+        <v>0.7972187187152801</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.6417525752133566</v>
+        <v>0.06670977092509321</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.501156825476262</v>
+        <v>0.9972187187152801</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.6417524556469398</v>
+        <v>0.06670965135867638</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.501156825476262</v>
+        <v>0.9972187187152801</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.6417524636180343</v>
+        <v>0.06670965932977083</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_3_000001.xlsx
+++ b/out/Attention-mamba2_repeat_3_000001.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.1828409880399704</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.140787574607127</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.3230682909488678</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.140787574607127</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.1811540275812149</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.140787574607127</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.1568424552679062</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.140787574607127</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.2158433347940445</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.140787574607127</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.3751057982444763</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.140787574607127</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.1820197850465775</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.140787574607127</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.1717970222234726</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.140787574607127</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.1877255588769913</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.140787574607127</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.1543925255537033</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.140787574607127</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.1714339107275009</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.140787574607127</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.1718450337648392</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.140787574607127</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.2318280786275864</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.140787574607127</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.4222660958766937</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.140787574607127</v>
+        <v>0.16</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.02174639329314232</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.2947854768329915</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.01664797961711884</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.2947854768329914</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.3232844769954681</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.2947854768329914</v>
+        <v>0.16</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.3720597326755524</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.9407875746071271</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.314591109752655</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.9407875746071271</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.100835770368576</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.140787574607127</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.1078802496194839</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.140787574607127</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.2170484513044357</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.140787574607127</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.4029147028923035</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.140787574607127</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.4335194528102875</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.140787574607127</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.2625784277915955</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.140787574607127</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.231277123093605</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.140787574607127</v>
+        <v>0.3</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.2010162621736526</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.140787574607127</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.1560273617506027</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.140787574607127</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.2102339118719101</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.2947854768329914</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.02064501121640205</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.2947854768329913</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.2182416766881943</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.2947854768329913</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.2905778586864471</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.9407875746071271</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.1826144754886627</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.9407875746071271</v>
+        <v>-0.3</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.1612138897180557</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.140787574607127</v>
+        <v>-0.16</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.1517728418111801</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.140787574607127</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.1776876449584961</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.140787574607127</v>
+        <v>-0.16</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.2014831155538559</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.140787574607127</v>
+        <v>-0.16</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.2160709053277969</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.4947854768329913</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.05492603778839111</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.2947854768329914</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.01408429071307182</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.2947854768329914</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.03705320879817009</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.9407875746071271</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>0.02910926565527916</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.9407875746071271</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC43" t="n">
-        <v>-2.31607684798073e-05</v>
+        <v>-0.0001702408744366839</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.009972354459690098</v>
+        <v>0.07330077777373428</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.01818319782614708</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.4947854768329913</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.01997132249682862</v>
+        <v>0.1467971759432526</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.03852765181264967</v>
+        <v>0.2831996698953014</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.05173390358686447</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.3512166209411444</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.08708142989710253</v>
+        <v>0.6400831868157596</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.01185183068427846</v>
+        <v>0.08711329698371349</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.05100726336240768</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.9972187187152801</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.07220700984759769</v>
+        <v>0.5307526231656382</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.002401416990871525</v>
+        <v>0.01767614252776867</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.02533545717597008</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.9972187187152801</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.06514287970358738</v>
+        <v>0.4788543111816319</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.002078387687239212</v>
+        <v>0.01530832500785563</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.04792866855859756</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.9972187187152801</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.06689682790407654</v>
+        <v>0.4917752774562403</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.001013525793800064</v>
+        <v>0.00748238961545394</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.009874824434518814</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.9972187187152801</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.06684332705114317</v>
+        <v>0.4914138391048955</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.0004814289328860417</v>
+        <v>0.003568381776201306</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.01458139345049858</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.9972187187152801</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.06679088396141189</v>
+        <v>0.4910602829844139</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.0001976425139068041</v>
+        <v>0.001483643082930753</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.002632319927215576</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.9972187187152801</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.06670418159370729</v>
+        <v>0.4904549732263382</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0001354442111847542</v>
+        <v>0.001026724782164925</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.02676480636000633</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.9972187187152801</v>
+        <v>-0.16</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.06677724401964061</v>
+        <v>0.4910236470363983</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>5.363011915345791e-05</v>
+        <v>0.0004260280188314653</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.005846142768859863</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.3512166209411443</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.06674890737445187</v>
+        <v>0.4908470842272644</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>2.506772249982401e-05</v>
+        <v>0.0002181693181098049</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.02007517591118813</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.1512166209411443</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.06674602046867716</v>
+        <v>0.4908576145057606</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>7.071873988355347e-06</v>
+        <v>8.265230243718883e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.02391123026609421</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.1512166209411443</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.06673439215506008</v>
+        <v>0.4908043437054495</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>1.298965874694778e-06</v>
+        <v>4.310119395221467e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.0009819567203521729</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.7972187187152801</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.06673047802515723</v>
+        <v>0.4908072705833183</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>-1.611969606870321e-06</v>
+        <v>1.871621275190775e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.02859104983508587</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.7972187187152801</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.06672537471617641</v>
+        <v>0.4908015474204531</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>-3.401523153206475e-06</v>
+        <v>6.189337927554673e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.02212383225560188</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.9972187187152801</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.06672017969676969</v>
+        <v>0.4907951822846045</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>-4.538828146730642e-06</v>
+        <v>-3.882814673064221e-07</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.01472490653395653</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.9972187187152801</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.06671496332559386</v>
+        <v>0.4907886642314969</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-4.586597321616299e-06</v>
+        <v>-2.932986608081494e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.01864778622984886</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.3512166209411443</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.06670986657822668</v>
+        <v>0.4907831326680945</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0</v>
+        <v>-4.04640701416283e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.0004746131598949432</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.1512166209411443</v>
+        <v>-0.16</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.06670977092509321</v>
+        <v>0.4907775558109437</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0</v>
+        <v>-4.817481666896968e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.01908458396792412</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.4947854768329915</v>
+        <v>-0.16</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.06670963541648746</v>
+        <v>0.4907721484682867</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0</v>
+        <v>-4.777674021158921e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.01030745729804039</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.1512166209411442</v>
+        <v>-0.16</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.06670967527195974</v>
+        <v>0.4907672273145653</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.02311097458004951</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.4947854768329915</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.06670971512743203</v>
+        <v>0.4907672671700376</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.001153867691755295</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.1512166209411442</v>
+        <v>-0.16</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.06670970715633756</v>
+        <v>0.4907672591989432</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.027276411652565</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.4947854768329915</v>
+        <v>-0.16</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.06670986657822668</v>
+        <v>0.4907674186208323</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.01498107239603996</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.1512166209411442</v>
+        <v>-0.3</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.06670977092509321</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.006157226860523224</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.1512166209411442</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.06671012165324949</v>
+        <v>0.4907676736958551</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.01788634061813354</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.3512166209411443</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.06670987454932113</v>
+        <v>0.4907674265919267</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.01561139151453972</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.3512166209411443</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.06670983469384885</v>
+        <v>0.4907673867364544</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.01918325200676918</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.3512166209411443</v>
+        <v>-0.3</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.06670977092509321</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.01763048395514488</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.9972187187152801</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.06670984266494331</v>
+        <v>0.4907673947075489</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.03325039148330688</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.3512166209411443</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.06670977092509321</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.01911568269133568</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.2947854768329914</v>
+        <v>-0.3</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.06670987454932113</v>
+        <v>0.4907674265919267</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.009508561342954636</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.4947854768329915</v>
+        <v>0.3</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.06670997020245484</v>
+        <v>0.4907675222450604</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.02841455489397049</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.1512166209411443</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.06670990643369895</v>
+        <v>0.4907674584763045</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.0144263468682766</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.1512166209411443</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.06670986657822668</v>
+        <v>0.4907674186208323</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.004226390272378922</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.3512166209411444</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.06670984266494331</v>
+        <v>0.4907673947075489</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.008166726678609848</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.3512166209411444</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.06670959556101519</v>
+        <v>0.4907671476036208</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.0289541631937027</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.9972187187152801</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.0667095158500704</v>
+        <v>0.490767067892676</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.05568575114011765</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.9972187187152801</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.06670956367663713</v>
+        <v>0.4907671157192427</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.02688959240913391</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.9972187187152801</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.06670968324305419</v>
+        <v>0.4907672352856598</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.05209406092762947</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.9972187187152801</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.06670966730086529</v>
+        <v>0.4907672193434709</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.03177082538604736</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.9972187187152801</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.06670968324305419</v>
+        <v>0.4907672352856598</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.02102792635560036</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.9972187187152801</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.06670966730086529</v>
+        <v>0.4907672193434709</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.04822291061282158</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.3512166209411444</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.06670972309852648</v>
+        <v>0.4907672751411321</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.008144684135913849</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.4947854768329915</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.06670972309852648</v>
+        <v>0.4907672751411321</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.004878733307123184</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.4947854768329915</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.06670972309852648</v>
+        <v>0.4907672751411321</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.02052595838904381</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.4947854768329913</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.06670987454932113</v>
+        <v>0.4907674265919267</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.03784842416644096</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.1512166209411444</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.06671008976887166</v>
+        <v>0.4907676418114773</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.04168616607785225</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.1512166209411444</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.06671000208683266</v>
+        <v>0.4907675541294382</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.02927327342331409</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.9972187187152801</v>
+        <v>-0.3</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.06670995426026592</v>
+        <v>0.4907675063028715</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.006408508867025375</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.9972187187152801</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.06671000208683266</v>
+        <v>0.4907675541294382</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.03011829219758511</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.9972187187152801</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.06670981875165995</v>
+        <v>0.4907673707942655</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.03492210805416107</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.9972187187152801</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.0667098267227544</v>
+        <v>0.49076737876536</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.03137272968888283</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.9972187187152801</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.06670983469384885</v>
+        <v>0.4907673867364544</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.03172633796930313</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.9972187187152801</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.06670984266494331</v>
+        <v>0.4907673947075489</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.01838172599673271</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.9972187187152801</v>
+        <v>0.3</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.06670984266494331</v>
+        <v>0.4907673947075489</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.01074345782399178</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.9972187187152801</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.06670988252041558</v>
+        <v>0.4907674345630212</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.01805973425507545</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.9972187187152801</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.06670994628917147</v>
+        <v>0.4907674983317771</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.002183042466640472</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.7972187187152801</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.06671005788449384</v>
+        <v>0.4907676099270994</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.01081320270895958</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.7972187187152801</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.06671010571106058</v>
+        <v>0.4907676577536662</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.01772690564393997</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.7972187187152801</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.06671006585558829</v>
+        <v>0.4907676178981939</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.013275396078825</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.7972187187152801</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.06670999411573819</v>
+        <v>0.4907675461583438</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.01525286585092545</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.1512166209411444</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.06671011368215503</v>
+        <v>0.4907676657247606</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.02365970984101295</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.1512166209411444</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.06670995426026592</v>
+        <v>0.4907675063028715</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.0175691694021225</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.1512166209411444</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.06670972309852648</v>
+        <v>0.4907672751411321</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.006927493959665298</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.7972187187152801</v>
+        <v>0.16</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.06670967527195974</v>
+        <v>0.4907672273145653</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.0206896997988224</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.7972187187152801</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.06670970715633756</v>
+        <v>0.4907672591989432</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.02846469357609749</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.9972187187152801</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.06670977092509321</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.03039177507162094</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.9972187187152801</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.06670977092509321</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.03977841883897781</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.9972187187152801</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.06670969121414866</v>
+        <v>0.4907672432567542</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.04836669564247131</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.9972187187152801</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.06670957164773159</v>
+        <v>0.4907671236903371</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.03072762116789818</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.9972187187152801</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.06670953179225932</v>
+        <v>0.4907670838348649</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.03928864374756813</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.9972187187152801</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.06670967527195974</v>
+        <v>0.4907672273145653</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.04511715844273567</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.9972187187152801</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.06670981078056548</v>
+        <v>0.4907673628231711</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.03137783333659172</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.7972187187152801</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.06670979483837658</v>
+        <v>0.4907673468809822</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.04518209397792816</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.7972187187152801</v>
+        <v>-0.16</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.06670977092509321</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.02475890330970287</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.7972187187152801</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.06670973106962093</v>
+        <v>0.4907672831122265</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.02951448783278465</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.1512166209411444</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.06670962744539301</v>
+        <v>0.4907671794879986</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.0136072002351284</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.1512166209411444</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.06670950787897595</v>
+        <v>0.4907670599215815</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.02907965146005154</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.1512166209411444</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.06670962744539301</v>
+        <v>0.4907671794879986</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.02208340540528297</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.7972187187152801</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.06670967527195974</v>
+        <v>0.4907672273145653</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.02866067178547382</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.7972187187152801</v>
+        <v>-0.16</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.06670977092509321</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.02421549893915653</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.9972187187152801</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.06670965135867638</v>
+        <v>0.4907672034012819</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.05134465917944908</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.9972187187152801</v>
+        <v>0.72</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.06670965932977083</v>
+        <v>0.4907672113723764</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_3_000001.xlsx
+++ b/out/Attention-mamba2_repeat_3_000001.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>-0.1828409880399704</v>
+        <v>-0.1824469119310379</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.9999999999999998</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>-0.3230682909488678</v>
+        <v>-0.3230201005935669</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.9999999999999998</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>-0.1811540275812149</v>
+        <v>-0.1808400005102158</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.9999999999999998</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>-0.1568424552679062</v>
+        <v>-0.1564900875091553</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.9999999999999998</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>-0.2158433347940445</v>
+        <v>-0.2154410630464554</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.9999999999999998</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>-0.3751057982444763</v>
+        <v>-0.3753151893615723</v>
       </c>
       <c r="JB7" t="n">
         <v>-0.9999999999999998</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>-0.1820197850465775</v>
+        <v>-0.1817354112863541</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.9999999999999998</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>-0.1717970222234726</v>
+        <v>-0.1714613288640976</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.9999999999999998</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>-0.1877255588769913</v>
+        <v>-0.1874538362026215</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.9999999999999998</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>-0.1543925255537033</v>
+        <v>-0.1540689915418625</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.9999999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>-0.1714339107275009</v>
+        <v>-0.1710923612117767</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.9999999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>-0.1718450337648392</v>
+        <v>-0.1715063899755478</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.9999999999999998</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>-0.2318280786275864</v>
+        <v>-0.2314485758543015</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.1199999999999999</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>-0.4222660958766937</v>
+        <v>-0.4235642552375793</v>
       </c>
       <c r="JB15" t="n">
         <v>0.16</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>-0.02174639329314232</v>
+        <v>-0.02316557243466377</v>
       </c>
       <c r="JB16" t="n">
         <v>0.1600000000000001</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0.01664797961711884</v>
+        <v>0.01508700847625732</v>
       </c>
       <c r="JB17" t="n">
         <v>0.1600000000000001</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>-0.3232844769954681</v>
+        <v>-0.3230697214603424</v>
       </c>
       <c r="JB18" t="n">
         <v>0.16</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>-0.3720597326755524</v>
+        <v>-0.3720240294933319</v>
       </c>
       <c r="JB19" t="n">
         <v>0.02000000000000007</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>-0.314591109752655</v>
+        <v>-0.3146044909954071</v>
       </c>
       <c r="JB20" t="n">
         <v>-0.1199999999999999</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>-0.100835770368576</v>
+        <v>-0.1005934029817581</v>
       </c>
       <c r="JB21" t="n">
         <v>-0.7199999999999999</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>-0.1078802496194839</v>
+        <v>-0.1076959818601608</v>
       </c>
       <c r="JB22" t="n">
         <v>-0.7199999999999999</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>-0.2170484513044357</v>
+        <v>-0.2168362587690353</v>
       </c>
       <c r="JB23" t="n">
         <v>-0.7199999999999999</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>-0.4029147028923035</v>
+        <v>-0.4028613269329071</v>
       </c>
       <c r="JB24" t="n">
         <v>-0.8599999999999999</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>-0.4335194528102875</v>
+        <v>-0.4337872564792633</v>
       </c>
       <c r="JB25" t="n">
         <v>-0.8599999999999999</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>-0.2625784277915955</v>
+        <v>-0.2623324990272522</v>
       </c>
       <c r="JB26" t="n">
         <v>-0.5799999999999998</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>-0.231277123093605</v>
+        <v>-0.2310566157102585</v>
       </c>
       <c r="JB27" t="n">
         <v>0.3</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>-0.2010162621736526</v>
+        <v>-0.2007991522550583</v>
       </c>
       <c r="JB28" t="n">
         <v>0.5799999999999998</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>-0.1560273617506027</v>
+        <v>-0.1557766199111938</v>
       </c>
       <c r="JB29" t="n">
         <v>0.8599999999999999</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>-0.2102339118719101</v>
+        <v>-0.2098581343889236</v>
       </c>
       <c r="JB30" t="n">
         <v>0.8599999999999999</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0.02064501121640205</v>
+        <v>0.01941835880279541</v>
       </c>
       <c r="JB31" t="n">
         <v>0.5799999999999998</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>-0.2182416766881943</v>
+        <v>-0.2179048508405685</v>
       </c>
       <c r="JB32" t="n">
         <v>0.4399999999999999</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>-0.2905778586864471</v>
+        <v>-0.2904967069625854</v>
       </c>
       <c r="JB33" t="n">
         <v>0.4399999999999999</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>-0.1826144754886627</v>
+        <v>-0.1823006719350815</v>
       </c>
       <c r="JB34" t="n">
         <v>-0.3</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>-0.1612138897180557</v>
+        <v>-0.1609439700841904</v>
       </c>
       <c r="JB35" t="n">
         <v>-0.16</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>-0.1517728418111801</v>
+        <v>-0.1515155583620071</v>
       </c>
       <c r="JB36" t="n">
         <v>-0.02000000000000007</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>-0.1776876449584961</v>
+        <v>-0.1774372011423111</v>
       </c>
       <c r="JB37" t="n">
         <v>-0.16</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>-0.2014831155538559</v>
+        <v>-0.2012128680944443</v>
       </c>
       <c r="JB38" t="n">
         <v>-0.16</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>-0.2160709053277969</v>
+        <v>-0.2156126648187637</v>
       </c>
       <c r="JB39" t="n">
         <v>-0.02000000000000007</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.05492603778839111</v>
+        <v>0.05369685217738152</v>
       </c>
       <c r="JB40" t="n">
         <v>0.5799999999999998</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>-0.01408429071307182</v>
+        <v>-0.01408888027071953</v>
       </c>
       <c r="JB41" t="n">
         <v>0.7199999999999999</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>-0.03705320879817009</v>
+        <v>-0.03735646978020668</v>
       </c>
       <c r="JB42" t="n">
         <v>0.9999999999999998</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.02910926565527916</v>
+        <v>0.01658329367637634</v>
       </c>
       <c r="JB43" t="n">
         <v>0.8599999999999999</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>-0.01818319782614708</v>
+        <v>-0.04229674115777016</v>
       </c>
       <c r="JB44" t="n">
         <v>0.8599999999999999</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.05173390358686447</v>
+        <v>0.05032263696193695</v>
       </c>
       <c r="JB45" t="n">
         <v>0.8599999999999999</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0.05100726336240768</v>
+        <v>0.04956579580903053</v>
       </c>
       <c r="JB46" t="n">
         <v>0.8599999999999999</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0.02533545717597008</v>
+        <v>0.02395057305693626</v>
       </c>
       <c r="JB47" t="n">
         <v>0.8599999999999999</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0.04792866855859756</v>
+        <v>0.04678527265787125</v>
       </c>
       <c r="JB48" t="n">
         <v>0.8599999999999999</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0.009874824434518814</v>
+        <v>0.00875541940331459</v>
       </c>
       <c r="JB49" t="n">
         <v>0.1199999999999999</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0.01458139345049858</v>
+        <v>0.01359618082642555</v>
       </c>
       <c r="JB50" t="n">
         <v>0.1199999999999999</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0.002632319927215576</v>
+        <v>0.001704875379800797</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.02000000000000007</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0.02676480636000633</v>
+        <v>0.02586905658245087</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.16</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0.005846142768859863</v>
+        <v>0.004654072225093842</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.02000000000000007</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>-0.02007517591118813</v>
+        <v>-0.02120013162493706</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.02000000000000007</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0.02391123026609421</v>
+        <v>0.02301676198840141</v>
       </c>
       <c r="JB55" t="n">
         <v>-0.02000000000000007</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0.0009819567203521729</v>
+        <v>0.000164177268743515</v>
       </c>
       <c r="JB56" t="n">
         <v>0.1199999999999999</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0.02859104983508587</v>
+        <v>0.02809502743184566</v>
       </c>
       <c r="JB57" t="n">
         <v>0.8599999999999999</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.02212383225560188</v>
+        <v>0.02139164879918098</v>
       </c>
       <c r="JB58" t="n">
         <v>0.7199999999999999</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.01472490653395653</v>
+        <v>0.01397619396448135</v>
       </c>
       <c r="JB59" t="n">
         <v>0.7199999999999999</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0.01864778622984886</v>
+        <v>0.01785528287291527</v>
       </c>
       <c r="JB60" t="n">
         <v>0.5799999999999998</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>-0.0004746131598949432</v>
+        <v>-0.001372963190078735</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.16</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0.01908458396792412</v>
+        <v>0.01824020594358444</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.16</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>-0.01030745729804039</v>
+        <v>-0.01127328351140022</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.16</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0.02311097458004951</v>
+        <v>0.02230758965015411</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.02000000000000007</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>-0.001153867691755295</v>
+        <v>-0.002143707126379013</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.16</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.027276411652565</v>
+        <v>0.0263696163892746</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.16</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>-0.01498107239603996</v>
+        <v>-0.0160965658724308</v>
       </c>
       <c r="JB67" t="n">
         <v>-0.3</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0.006157226860523224</v>
+        <v>0.005214221775531769</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.4399999999999999</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0.01788634061813354</v>
+        <v>0.01702902093529701</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.5799999999999998</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>-0.01561139151453972</v>
+        <v>-0.01653960719704628</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.4399999999999999</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0.01918325200676918</v>
+        <v>0.01845420524477959</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.3</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0.01763048395514488</v>
+        <v>0.01686949282884598</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.4399999999999999</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0.03325039148330688</v>
+        <v>0.03227771818637848</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.4399999999999999</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>-0.01911568269133568</v>
+        <v>-0.02056201174855232</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.3</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>-0.009508561342954636</v>
+        <v>-0.01072434708476067</v>
       </c>
       <c r="JB75" t="n">
         <v>0.3</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0.02841455489397049</v>
+        <v>0.02759460359811783</v>
       </c>
       <c r="JB76" t="n">
         <v>0.02000000000000007</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.0144263468682766</v>
+        <v>0.01393647119402885</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.4399999999999999</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>-0.004226390272378922</v>
+        <v>-0.005225244909524918</v>
       </c>
       <c r="JB78" t="n">
         <v>0.4399999999999999</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.008166726678609848</v>
+        <v>0.007396947592496872</v>
       </c>
       <c r="JB79" t="n">
         <v>0.4399999999999999</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0.0289541631937027</v>
+        <v>0.02861197665333748</v>
       </c>
       <c r="JB80" t="n">
         <v>0.5799999999999998</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0.05568575114011765</v>
+        <v>0.05525936186313629</v>
       </c>
       <c r="JB81" t="n">
         <v>0.8599999999999999</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.02688959240913391</v>
+        <v>0.02616912126541138</v>
       </c>
       <c r="JB82" t="n">
         <v>0.9999999999999998</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0.05209406092762947</v>
+        <v>0.03235157206654549</v>
       </c>
       <c r="JB83" t="n">
         <v>0.8599999999999999</v>
@@ -67721,10 +67721,10 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0.03177082538604736</v>
+        <v>0.03138533979654312</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.7199999999999999</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC84" t="n">
         <v>0.4907672352856598</v>
@@ -68516,10 +68516,10 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.02102792635560036</v>
+        <v>0.02026229724287987</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="JC85" t="n">
         <v>0.4907672193434709</v>
@@ -69311,10 +69311,10 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.04822291061282158</v>
+        <v>0.005698297172784805</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC86" t="n">
         <v>0.4907672751411321</v>
@@ -70106,10 +70106,10 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>-0.008144684135913849</v>
+        <v>-0.002129044383764267</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.5799999999999998</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC87" t="n">
         <v>0.4907672751411321</v>
@@ -70901,10 +70901,10 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>-0.004878733307123184</v>
+        <v>-0.005974270403385162</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC88" t="n">
         <v>0.4907672751411321</v>
@@ -71696,10 +71696,10 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0.02052595838904381</v>
+        <v>0.01766748353838921</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC89" t="n">
         <v>0.4907674265919267</v>
@@ -72491,10 +72491,10 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>-0.03784842416644096</v>
+        <v>-0.0389409251511097</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.3</v>
       </c>
       <c r="JC90" t="n">
         <v>0.4907676418114773</v>
@@ -73286,10 +73286,10 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.04168616607785225</v>
+        <v>0.02239685505628586</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.16</v>
       </c>
       <c r="JC91" t="n">
         <v>0.4907675541294382</v>
@@ -74081,10 +74081,10 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.02927327342331409</v>
+        <v>0.01948025077581406</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.3</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC92" t="n">
         <v>0.4907675063028715</v>
@@ -74876,10 +74876,10 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.006408508867025375</v>
+        <v>0.005609169602394104</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.5799999999999998</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC93" t="n">
         <v>0.4907675541294382</v>
@@ -75671,10 +75671,10 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.03011829219758511</v>
+        <v>0.02972741611301899</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.5799999999999998</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC94" t="n">
         <v>0.4907673707942655</v>
@@ -76466,10 +76466,10 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0.03492210805416107</v>
+        <v>0.03435856848955154</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.5799999999999998</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC95" t="n">
         <v>0.49076737876536</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.03137272968888283</v>
+        <v>0.02130831032991409</v>
       </c>
       <c r="JB96" t="n">
         <v>0.7199999999999999</v>
@@ -78056,10 +78056,10 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.03172633796930313</v>
+        <v>0.03132893145084381</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC97" t="n">
         <v>0.4907673947075489</v>
@@ -78851,10 +78851,10 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.01838172599673271</v>
+        <v>0.01783385127782822</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.3</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC98" t="n">
         <v>0.4907673947075489</v>
@@ -79646,10 +79646,10 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0.01074345782399178</v>
+        <v>0.009779773652553558</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.3</v>
       </c>
       <c r="JC99" t="n">
         <v>0.4907674345630212</v>
@@ -80441,10 +80441,10 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.01805973425507545</v>
+        <v>0.01726049184799194</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC100" t="n">
         <v>0.4907674983317771</v>
@@ -81236,10 +81236,10 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.002183042466640472</v>
+        <v>0.001373730599880219</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC101" t="n">
         <v>0.4907676099270994</v>
@@ -82031,10 +82031,10 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.01081320270895958</v>
+        <v>0.01181589439511299</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.5799999999999998</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC102" t="n">
         <v>0.4907676577536662</v>
@@ -82826,10 +82826,10 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.01772690564393997</v>
+        <v>0.01695384457707405</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.5799999999999998</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC103" t="n">
         <v>0.4907676178981939</v>
@@ -83621,10 +83621,10 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.013275396078825</v>
+        <v>0.01248358935117722</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.5799999999999998</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC104" t="n">
         <v>0.4907675461583438</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.01525286585092545</v>
+        <v>0.01439641788601875</v>
       </c>
       <c r="JB105" t="n">
         <v>-0.4399999999999999</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>-0.02365970984101295</v>
+        <v>-0.0246150828897953</v>
       </c>
       <c r="JB106" t="n">
         <v>-0.5799999999999998</v>
@@ -86006,10 +86006,10 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0.0175691694021225</v>
+        <v>0.01681734248995781</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.02000000000000007</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC107" t="n">
         <v>0.4907672751411321</v>
@@ -86801,10 +86801,10 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0.006927493959665298</v>
+        <v>0.006198126822710037</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.16</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC108" t="n">
         <v>0.4907672273145653</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.0206896997988224</v>
+        <v>0.02024401351809502</v>
       </c>
       <c r="JB109" t="n">
         <v>0.4399999999999999</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.02846469357609749</v>
+        <v>0.0276959054172039</v>
       </c>
       <c r="JB110" t="n">
         <v>0.5799999999999998</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.03039177507162094</v>
+        <v>0.03003975190222263</v>
       </c>
       <c r="JB111" t="n">
         <v>0.8599999999999999</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.03977841883897781</v>
+        <v>0.03934862464666367</v>
       </c>
       <c r="JB112" t="n">
         <v>0.9999999999999998</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.04836669564247131</v>
+        <v>0.04792687296867371</v>
       </c>
       <c r="JB113" t="n">
         <v>0.9999999999999998</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.03072762116789818</v>
+        <v>0.03026527911424637</v>
       </c>
       <c r="JB114" t="n">
         <v>0.9999999999999998</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.03928864374756813</v>
+        <v>0.03186878189444542</v>
       </c>
       <c r="JB115" t="n">
         <v>0.8599999999999999</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.04511715844273567</v>
+        <v>0.04465437680482864</v>
       </c>
       <c r="JB116" t="n">
         <v>0.7199999999999999</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.03137783333659172</v>
+        <v>0.03081468120217323</v>
       </c>
       <c r="JB117" t="n">
         <v>-0.02000000000000007</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.04518209397792816</v>
+        <v>0.04466264694929123</v>
       </c>
       <c r="JB118" t="n">
         <v>-0.16</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.02475890330970287</v>
+        <v>0.02419209852814674</v>
       </c>
       <c r="JB119" t="n">
         <v>-0.4399999999999999</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.02951448783278465</v>
+        <v>0.02854327857494354</v>
       </c>
       <c r="JB120" t="n">
         <v>-0.4399999999999999</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>-0.0136072002351284</v>
+        <v>-0.01460579410195351</v>
       </c>
       <c r="JB121" t="n">
         <v>-0.4399999999999999</v>
@@ -97931,10 +97931,10 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.02907965146005154</v>
+        <v>0.02866757661104202</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.3</v>
       </c>
       <c r="JC122" t="n">
         <v>0.4907671794879986</v>
@@ -98726,10 +98726,10 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.02208340540528297</v>
+        <v>0.02128376066684723</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.3</v>
       </c>
       <c r="JC123" t="n">
         <v>0.4907672273145653</v>
@@ -99521,10 +99521,10 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.02866067178547382</v>
+        <v>0.02823221497237682</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.16</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC124" t="n">
         <v>0.4907673229676988</v>
@@ -100316,10 +100316,10 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0.02421549893915653</v>
+        <v>0.02362603880465031</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.5800000000000001</v>
+        <v>0.72</v>
       </c>
       <c r="JC125" t="n">
         <v>0.4907672034012819</v>
@@ -101111,10 +101111,10 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.05134465917944908</v>
+        <v>0.05030743777751923</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.72</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC126" t="n">
         <v>0.4907672113723764</v>
